--- a/dev/lci-case-study-daccs_storage_risk.xlsx
+++ b/dev/lci-case-study-daccs_storage_risk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="52.33203125" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -787,7 +786,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -795,16 +797,6 @@
       <c r="P14" t="n">
         <v>20</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>port</t>
@@ -846,7 +838,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -854,16 +849,6 @@
       <c r="P15" t="n">
         <v>20</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>port</t>
@@ -905,7 +890,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -913,16 +901,6 @@
       <c r="P16" t="n">
         <v>20</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>port</t>
@@ -964,7 +942,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -972,16 +953,6 @@
       <c r="P17" t="n">
         <v>20</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>[1,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>[0.08,0.12,0.16,0.2,0.2,0.16,0.08]</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>port</t>
@@ -1082,7 +1053,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1090,16 +1064,6 @@
       <c r="P19" t="n">
         <v>20</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>port</t>
@@ -1141,7 +1105,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -1149,16 +1116,6 @@
       <c r="P20" t="n">
         <v>20</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>port</t>
@@ -1195,7 +1152,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1203,16 +1163,6 @@
       <c r="P21" t="n">
         <v>20</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>[0,1,2,3,5,8,12,16,20]</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[0.06,0.07,0.08,0.1,0.12,0.15,0.16,0.14,0.12]</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>port</t>
@@ -1308,7 +1258,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -1316,16 +1269,6 @@
       <c r="P23" t="n">
         <v>20</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>[0,5,10,15,20]</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>[0.24,0.22,0.2,0.18,0.16]</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>port</t>
@@ -1419,7 +1362,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -1427,16 +1373,6 @@
       <c r="P25" t="n">
         <v>20</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>[0,1,2,5,10,15,20]</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>[0.22,0.16,0.12,0.12,0.14,0.12,0.12]</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>port</t>
@@ -1473,7 +1409,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -1481,16 +1420,6 @@
       <c r="P26" t="n">
         <v>20</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>[0,5,10,15,20]</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>[0.3,0.24,0.19,0.15,0.12]</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>port</t>
@@ -1527,23 +1456,16 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>20</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>[0,5,10,15,20]</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>[0.27,0.23,0.2,0.16,0.14]</t>
-        </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
